--- a/public/docs/Plantilla Cursos Extensión.xlsx
+++ b/public/docs/Plantilla Cursos Extensión.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://escuelanaval-my.sharepoint.com/personal/jestadisticaplen_enap_edu_co/Documents/Estadística/Plantillas Xertify/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="257" documentId="13_ncr:1_{BC3BDC5F-05B6-4C86-84AC-9E3B4D15C583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{651F0377-DEDB-458A-BE9A-1E375EB63FBF}"/>
+  <xr:revisionPtr revIDLastSave="270" documentId="13_ncr:1_{BC3BDC5F-05B6-4C86-84AC-9E3B4D15C583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57AEF430-EAAD-4D7F-AF76-556C305AB0DA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="974">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="973">
   <si>
     <t>Obligatorio</t>
   </si>
@@ -690,10 +690,6 @@
   </si>
   <si>
     <t>Opcional
-Fecha Fin</t>
-  </si>
-  <si>
-    <t>Opcional
 Fecha Inicio</t>
   </si>
   <si>
@@ -724,9 +720,6 @@
     <t>docformato</t>
   </si>
   <si>
-    <t>fechafin</t>
-  </si>
-  <si>
     <t>fechainicio</t>
   </si>
   <si>
@@ -2976,13 +2969,16 @@
   </si>
   <si>
     <t>December 31st, 2025</t>
+  </si>
+  <si>
+    <t>Validación</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -3035,6 +3031,13 @@
       <color rgb="FF0563C1"/>
       <name val="Aptos"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -3284,7 +3287,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3415,6 +3418,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4242,7 +4246,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>FECHA INICIO CURSO</a:t>
+            <a:t>FECHA INICIO Y FIN CURSO</a:t>
           </a:r>
           <a:br>
             <a:rPr lang="es-CO" sz="1100" b="1" baseline="0">
@@ -4259,105 +4263,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>(Ejemplo: 05 de mayo de 2025)</a:t>
-          </a:r>
-          <a:endParaRPr lang="es-CO" sz="1100" b="0">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-            <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="CuadroTexto 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC111E91-FC70-2E1E-D591-1A369C47F238}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16436340" y="731520"/>
-          <a:ext cx="2026920" cy="434340"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="bg1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-CO" sz="1100" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>FECHA FIN CURSO</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="es-CO" sz="1100" b="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="es-CO" sz="1100" b="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>(Ejemplo: 06 de mayo de 2025)</a:t>
+            <a:t>(Ejemplo: 5 al 6 de mayo de 2025)</a:t>
           </a:r>
           <a:endParaRPr lang="es-CO" sz="1100" b="0">
             <a:solidFill>
@@ -4470,13 +4376,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -4568,13 +4474,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -4666,13 +4572,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -4764,13 +4670,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>220980</xdr:rowOff>
@@ -4846,13 +4752,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>220980</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
@@ -4928,13 +4834,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>25</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>220980</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
@@ -5010,13 +4916,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>25</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>792480</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>220980</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
@@ -5190,13 +5096,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -5288,14 +5194,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1030940</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>1506070</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -5312,8 +5218,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11878235" y="0"/>
-          <a:ext cx="1506071" cy="448235"/>
+          <a:off x="18539011" y="0"/>
+          <a:ext cx="1515035" cy="448235"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5385,10 +5291,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5689,7 +5591,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:AA3"/>
+  <dimension ref="A1:Z3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.8984375" style="11" customWidth="1"/>
@@ -5707,17 +5609,17 @@
     <col min="16" max="16" width="21.59765625" style="8" customWidth="1"/>
     <col min="17" max="17" width="29.3984375" style="8" customWidth="1"/>
     <col min="18" max="18" width="19.8984375" style="43" customWidth="1"/>
-    <col min="19" max="21" width="27.69921875" style="8" customWidth="1"/>
-    <col min="22" max="22" width="31.3984375" style="8" customWidth="1"/>
-    <col min="23" max="23" width="34" style="8" customWidth="1"/>
-    <col min="24" max="24" width="31.3984375" style="8" customWidth="1"/>
-    <col min="25" max="25" width="9.69921875" style="35" customWidth="1"/>
-    <col min="26" max="26" width="9.69921875" style="39" customWidth="1"/>
-    <col min="27" max="27" width="9.69921875" style="22" customWidth="1"/>
-    <col min="28" max="16384" width="10.5" style="3"/>
+    <col min="19" max="20" width="27.69921875" style="8" customWidth="1"/>
+    <col min="21" max="21" width="31.3984375" style="8" customWidth="1"/>
+    <col min="22" max="22" width="34" style="8" customWidth="1"/>
+    <col min="23" max="23" width="31.3984375" style="8" customWidth="1"/>
+    <col min="24" max="24" width="9.69921875" style="35" customWidth="1"/>
+    <col min="25" max="25" width="9.69921875" style="39" customWidth="1"/>
+    <col min="26" max="26" width="9.69921875" style="22" customWidth="1"/>
+    <col min="27" max="16384" width="10.5" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -5764,43 +5666,40 @@
         <v>214</v>
       </c>
       <c r="P1" s="12" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="Q1" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="R1" s="40" t="s">
+        <v>216</v>
+      </c>
+      <c r="S1" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="T1" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="U1" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="V1" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="S1" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="T1" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="U1" s="16" t="s">
-        <v>236</v>
-      </c>
-      <c r="V1" s="16" t="s">
-        <v>234</v>
-      </c>
       <c r="W1" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="X1" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="Y1" s="36" t="s">
         <v>218</v>
       </c>
-      <c r="X1" s="16" t="s">
-        <v>235</v>
-      </c>
-      <c r="Y1" s="32" t="s">
+      <c r="Z1" s="20" t="s">
         <v>220</v>
       </c>
-      <c r="Z1" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="AA1" s="20" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:26" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>3</v>
       </c>
@@ -5844,46 +5743,43 @@
         <v>16</v>
       </c>
       <c r="O2" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q2" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="R2" s="41" t="s">
+        <v>224</v>
+      </c>
+      <c r="S2" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="P2" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q2" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="R2" s="41" t="s">
+      <c r="T2" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="U2" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="V2" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="W2" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="S2" s="17" t="s">
-        <v>225</v>
-      </c>
-      <c r="T2" s="17" t="s">
-        <v>224</v>
-      </c>
-      <c r="U2" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="V2" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="W2" s="17" t="s">
+      <c r="X2" s="33" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y2" s="37" t="s">
         <v>227</v>
       </c>
-      <c r="X2" s="17" t="s">
-        <v>228</v>
-      </c>
-      <c r="Y2" s="33" t="s">
-        <v>230</v>
-      </c>
-      <c r="Z2" s="37" t="s">
+      <c r="Z2" s="21" t="s">
         <v>229</v>
       </c>
-      <c r="AA2" s="21" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="23"/>
       <c r="B3" s="24"/>
       <c r="C3" s="30"/>
@@ -5907,15 +5803,14 @@
       <c r="U3" s="24"/>
       <c r="V3" s="24"/>
       <c r="W3" s="24"/>
-      <c r="X3" s="24"/>
-      <c r="Y3" s="34"/>
-      <c r="Z3" s="38"/>
-      <c r="AA3" s="29"/>
+      <c r="X3" s="34"/>
+      <c r="Y3" s="38"/>
+      <c r="Z3" s="29"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="tfh3YbVMsSK7Hvh5iQGDfR1/Tbm24/y2Xnw9pA4IO3RTvoD5ejm3mAlgrKoQsAlEBHSXYEfgzSQ2M19veNXodQ==" saltValue="T4K6uMQ3ZgCcGMm0Y7j1Xw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="oRHisi8i6cl25vIdOGc5S6pQT1PrOi33JBM6FxjQdwp4cyXeFjS1kqQeY5oAtVhRbnRiL8IK/sY3O6bFfNU1OA==" saltValue="WMhulMvucZopm2IUsk/VWg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
-    <protectedRange sqref="A3:AA422" name="Rango1"/>
+    <protectedRange sqref="A3:Z422" name="Rango1"/>
   </protectedRanges>
   <conditionalFormatting sqref="O3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
@@ -5961,7 +5856,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="C2:M367"/>
+  <dimension ref="C1:M367"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="10.5" customWidth="1"/>
@@ -5972,9 +5867,14 @@
     <col min="13" max="13" width="17.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="E1" s="46" t="s">
+        <v>972</v>
+      </c>
+    </row>
     <row r="2" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
     </row>
     <row r="3" spans="3:13" x14ac:dyDescent="0.3">
       <c r="D3" s="1" t="s">
@@ -5985,13 +5885,13 @@
       </c>
       <c r="G3" s="1"/>
       <c r="I3" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L3" s="45" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="M3" s="45" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="4" spans="3:13" x14ac:dyDescent="0.3">
@@ -6002,13 +5902,13 @@
         <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L4" s="45" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="M4" s="45" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="5" spans="3:13" x14ac:dyDescent="0.3">
@@ -6019,13 +5919,13 @@
         <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L5" s="45" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M5" s="45" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="6" spans="3:13" x14ac:dyDescent="0.3">
@@ -6033,13 +5933,13 @@
         <v>24</v>
       </c>
       <c r="I6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="L6" s="45" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="M6" s="45" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="7" spans="3:13" x14ac:dyDescent="0.3">
@@ -6047,13 +5947,13 @@
         <v>25</v>
       </c>
       <c r="I7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="L7" s="45" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="M7" s="45" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="8" spans="3:13" x14ac:dyDescent="0.3">
@@ -6061,10 +5961,10 @@
         <v>26</v>
       </c>
       <c r="L8" s="45" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M8" s="45" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="9" spans="3:13" x14ac:dyDescent="0.3">
@@ -6072,10 +5972,10 @@
         <v>27</v>
       </c>
       <c r="L9" s="45" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M9" s="45" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="10" spans="3:13" x14ac:dyDescent="0.3">
@@ -6083,24 +5983,24 @@
         <v>28</v>
       </c>
       <c r="L10" s="45" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M10" s="45" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="11" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D11" t="s">
         <v>29</v>
       </c>
       <c r="L11" s="45" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="M11" s="45" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="12" spans="3:13" x14ac:dyDescent="0.3">
@@ -6108,10 +6008,10 @@
         <v>30</v>
       </c>
       <c r="L12" s="45" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M12" s="45" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="13" spans="3:13" x14ac:dyDescent="0.3">
@@ -6119,10 +6019,10 @@
         <v>31</v>
       </c>
       <c r="L13" s="45" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M13" s="45" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="14" spans="3:13" x14ac:dyDescent="0.3">
@@ -6130,10 +6030,10 @@
         <v>32</v>
       </c>
       <c r="L14" s="45" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="M14" s="45" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="15" spans="3:13" x14ac:dyDescent="0.3">
@@ -6141,10 +6041,10 @@
         <v>33</v>
       </c>
       <c r="L15" s="45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="M15" s="45" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="16" spans="3:13" x14ac:dyDescent="0.3">
@@ -6152,10 +6052,10 @@
         <v>34</v>
       </c>
       <c r="L16" s="45" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M16" s="45" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="17" spans="3:13" x14ac:dyDescent="0.3">
@@ -6163,10 +6063,10 @@
         <v>35</v>
       </c>
       <c r="L17" s="45" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="M17" s="45" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="18" spans="3:13" x14ac:dyDescent="0.3">
@@ -6174,24 +6074,24 @@
         <v>36</v>
       </c>
       <c r="L18" s="45" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="M18" s="45" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="19" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D19" t="s">
         <v>37</v>
       </c>
       <c r="L19" s="45" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="M19" s="45" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="20" spans="3:13" x14ac:dyDescent="0.3">
@@ -6199,10 +6099,10 @@
         <v>38</v>
       </c>
       <c r="L20" s="45" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="M20" s="45" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="21" spans="3:13" x14ac:dyDescent="0.3">
@@ -6210,10 +6110,10 @@
         <v>39</v>
       </c>
       <c r="L21" s="45" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="M21" s="45" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="22" spans="3:13" x14ac:dyDescent="0.3">
@@ -6221,10 +6121,10 @@
         <v>40</v>
       </c>
       <c r="L22" s="45" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M22" s="45" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="23" spans="3:13" x14ac:dyDescent="0.3">
@@ -6232,10 +6132,10 @@
         <v>41</v>
       </c>
       <c r="L23" s="45" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="M23" s="45" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="24" spans="3:13" x14ac:dyDescent="0.3">
@@ -6243,10 +6143,10 @@
         <v>42</v>
       </c>
       <c r="L24" s="45" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="M24" s="45" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="25" spans="3:13" x14ac:dyDescent="0.3">
@@ -6254,10 +6154,10 @@
         <v>43</v>
       </c>
       <c r="L25" s="45" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="M25" s="45" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="26" spans="3:13" x14ac:dyDescent="0.3">
@@ -6265,10 +6165,10 @@
         <v>44</v>
       </c>
       <c r="L26" s="45" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="M26" s="45" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="27" spans="3:13" x14ac:dyDescent="0.3">
@@ -6276,24 +6176,24 @@
         <v>45</v>
       </c>
       <c r="L27" s="45" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="M27" s="45" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="28" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D28" t="s">
         <v>46</v>
       </c>
       <c r="L28" s="45" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M28" s="45" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="29" spans="3:13" x14ac:dyDescent="0.3">
@@ -6301,10 +6201,10 @@
         <v>47</v>
       </c>
       <c r="L29" s="45" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="M29" s="45" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="30" spans="3:13" x14ac:dyDescent="0.3">
@@ -6312,10 +6212,10 @@
         <v>48</v>
       </c>
       <c r="L30" s="45" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M30" s="45" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="31" spans="3:13" x14ac:dyDescent="0.3">
@@ -6323,10 +6223,10 @@
         <v>49</v>
       </c>
       <c r="L31" s="45" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M31" s="45" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="32" spans="3:13" x14ac:dyDescent="0.3">
@@ -6334,24 +6234,24 @@
         <v>50</v>
       </c>
       <c r="L32" s="45" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="M32" s="45" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="33" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
       </c>
       <c r="L33" s="45" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="M33" s="45" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="34" spans="3:13" x14ac:dyDescent="0.3">
@@ -6359,10 +6259,10 @@
         <v>51</v>
       </c>
       <c r="L34" s="45" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="M34" s="45" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="35" spans="3:13" x14ac:dyDescent="0.3">
@@ -6370,10 +6270,10 @@
         <v>52</v>
       </c>
       <c r="L35" s="45" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="M35" s="45" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="36" spans="3:13" x14ac:dyDescent="0.3">
@@ -6381,10 +6281,10 @@
         <v>53</v>
       </c>
       <c r="L36" s="45" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="M36" s="45" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="37" spans="3:13" x14ac:dyDescent="0.3">
@@ -6392,10 +6292,10 @@
         <v>54</v>
       </c>
       <c r="L37" s="45" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="M37" s="45" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="38" spans="3:13" x14ac:dyDescent="0.3">
@@ -6403,24 +6303,24 @@
         <v>55</v>
       </c>
       <c r="L38" s="45" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M38" s="45" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="39" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C39" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D39" t="s">
         <v>56</v>
       </c>
       <c r="L39" s="45" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="M39" s="45" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="40" spans="3:13" x14ac:dyDescent="0.3">
@@ -6428,24 +6328,24 @@
         <v>57</v>
       </c>
       <c r="L40" s="45" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="M40" s="45" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="41" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C41" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D41" t="s">
         <v>58</v>
       </c>
       <c r="L41" s="45" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="M41" s="45" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="42" spans="3:13" x14ac:dyDescent="0.3">
@@ -6453,10 +6353,10 @@
         <v>213</v>
       </c>
       <c r="L42" s="45" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="M42" s="45" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="43" spans="3:13" x14ac:dyDescent="0.3">
@@ -6464,10 +6364,10 @@
         <v>59</v>
       </c>
       <c r="L43" s="45" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="M43" s="45" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
     </row>
     <row r="44" spans="3:13" x14ac:dyDescent="0.3">
@@ -6475,24 +6375,24 @@
         <v>60</v>
       </c>
       <c r="L44" s="45" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="M44" s="45" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="45" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C45" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D45" t="s">
         <v>61</v>
       </c>
       <c r="L45" s="45" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="M45" s="45" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="46" spans="3:13" x14ac:dyDescent="0.3">
@@ -6500,10 +6400,10 @@
         <v>62</v>
       </c>
       <c r="L46" s="45" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M46" s="45" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="47" spans="3:13" x14ac:dyDescent="0.3">
@@ -6511,10 +6411,10 @@
         <v>63</v>
       </c>
       <c r="L47" s="45" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="M47" s="45" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="48" spans="3:13" x14ac:dyDescent="0.3">
@@ -6522,10 +6422,10 @@
         <v>64</v>
       </c>
       <c r="L48" s="45" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="M48" s="45" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="49" spans="3:13" x14ac:dyDescent="0.3">
@@ -6533,24 +6433,24 @@
         <v>65</v>
       </c>
       <c r="L49" s="45" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M49" s="45" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="50" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C50" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D50" t="s">
         <v>66</v>
       </c>
       <c r="L50" s="45" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="M50" s="45" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="51" spans="3:13" x14ac:dyDescent="0.3">
@@ -6558,10 +6458,10 @@
         <v>67</v>
       </c>
       <c r="L51" s="45" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="M51" s="45" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="52" spans="3:13" x14ac:dyDescent="0.3">
@@ -6569,10 +6469,10 @@
         <v>68</v>
       </c>
       <c r="L52" s="45" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M52" s="45" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="53" spans="3:13" x14ac:dyDescent="0.3">
@@ -6580,10 +6480,10 @@
         <v>69</v>
       </c>
       <c r="L53" s="45" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="M53" s="45" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="54" spans="3:13" x14ac:dyDescent="0.3">
@@ -6591,10 +6491,10 @@
         <v>70</v>
       </c>
       <c r="L54" s="45" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="M54" s="45" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
     </row>
     <row r="55" spans="3:13" x14ac:dyDescent="0.3">
@@ -6602,10 +6502,10 @@
         <v>71</v>
       </c>
       <c r="L55" s="45" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="M55" s="45" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="56" spans="3:13" x14ac:dyDescent="0.3">
@@ -6613,10 +6513,10 @@
         <v>72</v>
       </c>
       <c r="L56" s="45" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="M56" s="45" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
     </row>
     <row r="57" spans="3:13" x14ac:dyDescent="0.3">
@@ -6624,24 +6524,24 @@
         <v>73</v>
       </c>
       <c r="L57" s="45" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M57" s="45" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="58" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C58" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D58" t="s">
         <v>74</v>
       </c>
       <c r="L58" s="45" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="M58" s="45" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="59" spans="3:13" x14ac:dyDescent="0.3">
@@ -6649,10 +6549,10 @@
         <v>75</v>
       </c>
       <c r="L59" s="45" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="M59" s="45" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="60" spans="3:13" x14ac:dyDescent="0.3">
@@ -6660,10 +6560,10 @@
         <v>76</v>
       </c>
       <c r="L60" s="45" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="M60" s="45" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="61" spans="3:13" x14ac:dyDescent="0.3">
@@ -6671,24 +6571,24 @@
         <v>77</v>
       </c>
       <c r="L61" s="45" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="M61" s="45" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="62" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C62" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D62" t="s">
         <v>78</v>
       </c>
       <c r="L62" s="45" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="M62" s="45" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="63" spans="3:13" x14ac:dyDescent="0.3">
@@ -6696,10 +6596,10 @@
         <v>79</v>
       </c>
       <c r="L63" s="45" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="M63" s="45" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="64" spans="3:13" x14ac:dyDescent="0.3">
@@ -6707,10 +6607,10 @@
         <v>80</v>
       </c>
       <c r="L64" s="45" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="M64" s="45" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="65" spans="3:13" x14ac:dyDescent="0.3">
@@ -6718,10 +6618,10 @@
         <v>81</v>
       </c>
       <c r="L65" s="45" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="M65" s="45" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="66" spans="3:13" x14ac:dyDescent="0.3">
@@ -6729,10 +6629,10 @@
         <v>82</v>
       </c>
       <c r="L66" s="45" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="M66" s="45" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="67" spans="3:13" x14ac:dyDescent="0.3">
@@ -6740,10 +6640,10 @@
         <v>83</v>
       </c>
       <c r="L67" s="45" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="M67" s="45" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="68" spans="3:13" x14ac:dyDescent="0.3">
@@ -6751,10 +6651,10 @@
         <v>84</v>
       </c>
       <c r="L68" s="45" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M68" s="45" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="69" spans="3:13" x14ac:dyDescent="0.3">
@@ -6762,10 +6662,10 @@
         <v>85</v>
       </c>
       <c r="L69" s="45" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="M69" s="45" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="70" spans="3:13" x14ac:dyDescent="0.3">
@@ -6773,10 +6673,10 @@
         <v>86</v>
       </c>
       <c r="L70" s="45" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="M70" s="45" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="71" spans="3:13" x14ac:dyDescent="0.3">
@@ -6784,10 +6684,10 @@
         <v>87</v>
       </c>
       <c r="L71" s="45" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="M71" s="45" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="72" spans="3:13" x14ac:dyDescent="0.3">
@@ -6795,10 +6695,10 @@
         <v>88</v>
       </c>
       <c r="L72" s="45" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="M72" s="45" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="73" spans="3:13" x14ac:dyDescent="0.3">
@@ -6806,10 +6706,10 @@
         <v>89</v>
       </c>
       <c r="L73" s="45" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M73" s="45" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="74" spans="3:13" x14ac:dyDescent="0.3">
@@ -6817,10 +6717,10 @@
         <v>90</v>
       </c>
       <c r="L74" s="45" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="M74" s="45" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="75" spans="3:13" x14ac:dyDescent="0.3">
@@ -6828,24 +6728,24 @@
         <v>91</v>
       </c>
       <c r="L75" s="45" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="M75" s="45" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="76" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C76" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D76" t="s">
         <v>92</v>
       </c>
       <c r="L76" s="45" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="M76" s="45" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="77" spans="3:13" x14ac:dyDescent="0.3">
@@ -6853,10 +6753,10 @@
         <v>93</v>
       </c>
       <c r="L77" s="45" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="M77" s="45" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
     <row r="78" spans="3:13" x14ac:dyDescent="0.3">
@@ -6864,10 +6764,10 @@
         <v>94</v>
       </c>
       <c r="L78" s="45" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="M78" s="45" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="79" spans="3:13" x14ac:dyDescent="0.3">
@@ -6875,10 +6775,10 @@
         <v>95</v>
       </c>
       <c r="L79" s="45" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="M79" s="45" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="80" spans="3:13" x14ac:dyDescent="0.3">
@@ -6886,10 +6786,10 @@
         <v>96</v>
       </c>
       <c r="L80" s="45" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="M80" s="45" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="81" spans="4:13" x14ac:dyDescent="0.3">
@@ -6897,10 +6797,10 @@
         <v>97</v>
       </c>
       <c r="L81" s="45" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="M81" s="45" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="82" spans="4:13" x14ac:dyDescent="0.3">
@@ -6908,10 +6808,10 @@
         <v>98</v>
       </c>
       <c r="L82" s="45" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="M82" s="45" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="83" spans="4:13" x14ac:dyDescent="0.3">
@@ -6919,10 +6819,10 @@
         <v>99</v>
       </c>
       <c r="L83" s="45" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M83" s="45" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
     </row>
     <row r="84" spans="4:13" x14ac:dyDescent="0.3">
@@ -6930,10 +6830,10 @@
         <v>100</v>
       </c>
       <c r="L84" s="45" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="M84" s="45" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="85" spans="4:13" x14ac:dyDescent="0.3">
@@ -6941,10 +6841,10 @@
         <v>101</v>
       </c>
       <c r="L85" s="45" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="M85" s="45" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="86" spans="4:13" x14ac:dyDescent="0.3">
@@ -6952,10 +6852,10 @@
         <v>102</v>
       </c>
       <c r="L86" s="45" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="M86" s="45" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
     </row>
     <row r="87" spans="4:13" x14ac:dyDescent="0.3">
@@ -6963,10 +6863,10 @@
         <v>103</v>
       </c>
       <c r="L87" s="45" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="M87" s="45" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="88" spans="4:13" x14ac:dyDescent="0.3">
@@ -6974,10 +6874,10 @@
         <v>104</v>
       </c>
       <c r="L88" s="45" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="M88" s="45" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
     </row>
     <row r="89" spans="4:13" x14ac:dyDescent="0.3">
@@ -6985,10 +6885,10 @@
         <v>105</v>
       </c>
       <c r="L89" s="45" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="M89" s="45" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="90" spans="4:13" x14ac:dyDescent="0.3">
@@ -6996,10 +6896,10 @@
         <v>106</v>
       </c>
       <c r="L90" s="45" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="M90" s="45" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
     </row>
     <row r="91" spans="4:13" x14ac:dyDescent="0.3">
@@ -7007,10 +6907,10 @@
         <v>107</v>
       </c>
       <c r="L91" s="45" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="M91" s="45" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="92" spans="4:13" x14ac:dyDescent="0.3">
@@ -7018,10 +6918,10 @@
         <v>108</v>
       </c>
       <c r="L92" s="45" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M92" s="45" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
     </row>
     <row r="93" spans="4:13" x14ac:dyDescent="0.3">
@@ -7029,10 +6929,10 @@
         <v>109</v>
       </c>
       <c r="L93" s="45" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="M93" s="45" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="94" spans="4:13" x14ac:dyDescent="0.3">
@@ -7040,10 +6940,10 @@
         <v>110</v>
       </c>
       <c r="L94" s="45" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="M94" s="45" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="95" spans="4:13" x14ac:dyDescent="0.3">
@@ -7051,10 +6951,10 @@
         <v>111</v>
       </c>
       <c r="L95" s="45" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="M95" s="45" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="96" spans="4:13" x14ac:dyDescent="0.3">
@@ -7062,10 +6962,10 @@
         <v>112</v>
       </c>
       <c r="L96" s="45" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="M96" s="45" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
     </row>
     <row r="97" spans="3:13" x14ac:dyDescent="0.3">
@@ -7073,10 +6973,10 @@
         <v>113</v>
       </c>
       <c r="L97" s="45" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="M97" s="45" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="98" spans="3:13" x14ac:dyDescent="0.3">
@@ -7084,10 +6984,10 @@
         <v>114</v>
       </c>
       <c r="L98" s="45" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="M98" s="45" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
     </row>
     <row r="99" spans="3:13" x14ac:dyDescent="0.3">
@@ -7095,10 +6995,10 @@
         <v>115</v>
       </c>
       <c r="L99" s="45" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="M99" s="45" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="100" spans="3:13" x14ac:dyDescent="0.3">
@@ -7106,10 +7006,10 @@
         <v>116</v>
       </c>
       <c r="L100" s="45" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="M100" s="45" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
     </row>
     <row r="101" spans="3:13" x14ac:dyDescent="0.3">
@@ -7117,10 +7017,10 @@
         <v>117</v>
       </c>
       <c r="L101" s="45" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="M101" s="45" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="102" spans="3:13" x14ac:dyDescent="0.3">
@@ -7128,10 +7028,10 @@
         <v>118</v>
       </c>
       <c r="L102" s="45" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="M102" s="45" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
     </row>
     <row r="103" spans="3:13" x14ac:dyDescent="0.3">
@@ -7139,10 +7039,10 @@
         <v>119</v>
       </c>
       <c r="L103" s="45" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="M103" s="45" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="104" spans="3:13" x14ac:dyDescent="0.3">
@@ -7150,10 +7050,10 @@
         <v>120</v>
       </c>
       <c r="L104" s="45" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="M104" s="45" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
     </row>
     <row r="105" spans="3:13" x14ac:dyDescent="0.3">
@@ -7161,24 +7061,24 @@
         <v>121</v>
       </c>
       <c r="L105" s="45" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="M105" s="45" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="106" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C106" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D106" t="s">
         <v>122</v>
       </c>
       <c r="L106" s="45" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M106" s="45" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="107" spans="3:13" x14ac:dyDescent="0.3">
@@ -7186,10 +7086,10 @@
         <v>123</v>
       </c>
       <c r="L107" s="45" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="M107" s="45" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
     </row>
     <row r="108" spans="3:13" x14ac:dyDescent="0.3">
@@ -7197,10 +7097,10 @@
         <v>124</v>
       </c>
       <c r="L108" s="45" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="M108" s="45" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
     </row>
     <row r="109" spans="3:13" x14ac:dyDescent="0.3">
@@ -7208,10 +7108,10 @@
         <v>125</v>
       </c>
       <c r="L109" s="45" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="M109" s="45" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="110" spans="3:13" x14ac:dyDescent="0.3">
@@ -7219,10 +7119,10 @@
         <v>126</v>
       </c>
       <c r="L110" s="45" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="M110" s="45" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
     </row>
     <row r="111" spans="3:13" x14ac:dyDescent="0.3">
@@ -7230,10 +7130,10 @@
         <v>127</v>
       </c>
       <c r="L111" s="45" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="M111" s="45" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="112" spans="3:13" x14ac:dyDescent="0.3">
@@ -7241,10 +7141,10 @@
         <v>128</v>
       </c>
       <c r="L112" s="45" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="M112" s="45" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="113" spans="3:13" x14ac:dyDescent="0.3">
@@ -7252,10 +7152,10 @@
         <v>129</v>
       </c>
       <c r="L113" s="45" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="M113" s="45" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="114" spans="3:13" x14ac:dyDescent="0.3">
@@ -7263,24 +7163,24 @@
         <v>130</v>
       </c>
       <c r="L114" s="45" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="M114" s="45" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="115" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C115" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D115" t="s">
         <v>131</v>
       </c>
       <c r="L115" s="45" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="M115" s="45" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
     </row>
     <row r="116" spans="3:13" x14ac:dyDescent="0.3">
@@ -7288,10 +7188,10 @@
         <v>132</v>
       </c>
       <c r="L116" s="45" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="M116" s="45" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="117" spans="3:13" x14ac:dyDescent="0.3">
@@ -7299,10 +7199,10 @@
         <v>133</v>
       </c>
       <c r="L117" s="45" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="M117" s="45" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
     <row r="118" spans="3:13" x14ac:dyDescent="0.3">
@@ -7310,10 +7210,10 @@
         <v>134</v>
       </c>
       <c r="L118" s="45" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="M118" s="45" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="119" spans="3:13" x14ac:dyDescent="0.3">
@@ -7321,10 +7221,10 @@
         <v>135</v>
       </c>
       <c r="L119" s="45" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="M119" s="45" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="120" spans="3:13" x14ac:dyDescent="0.3">
@@ -7332,10 +7232,10 @@
         <v>136</v>
       </c>
       <c r="L120" s="45" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="M120" s="45" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
     </row>
     <row r="121" spans="3:13" x14ac:dyDescent="0.3">
@@ -7343,10 +7243,10 @@
         <v>137</v>
       </c>
       <c r="L121" s="45" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="M121" s="45" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
     </row>
     <row r="122" spans="3:13" x14ac:dyDescent="0.3">
@@ -7354,10 +7254,10 @@
         <v>138</v>
       </c>
       <c r="L122" s="45" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="M122" s="45" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="123" spans="3:13" x14ac:dyDescent="0.3">
@@ -7365,10 +7265,10 @@
         <v>139</v>
       </c>
       <c r="L123" s="45" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="M123" s="45" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="124" spans="3:13" x14ac:dyDescent="0.3">
@@ -7376,10 +7276,10 @@
         <v>140</v>
       </c>
       <c r="L124" s="45" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="M124" s="45" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="125" spans="3:13" x14ac:dyDescent="0.3">
@@ -7387,24 +7287,24 @@
         <v>141</v>
       </c>
       <c r="L125" s="45" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="M125" s="45" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="126" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C126" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D126" t="s">
         <v>142</v>
       </c>
       <c r="L126" s="45" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="M126" s="45" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
     </row>
     <row r="127" spans="3:13" x14ac:dyDescent="0.3">
@@ -7412,10 +7312,10 @@
         <v>143</v>
       </c>
       <c r="L127" s="45" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="M127" s="45" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="128" spans="3:13" x14ac:dyDescent="0.3">
@@ -7423,24 +7323,24 @@
         <v>144</v>
       </c>
       <c r="L128" s="45" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="M128" s="45" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
     </row>
     <row r="129" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C129" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D129" t="s">
         <v>145</v>
       </c>
       <c r="L129" s="45" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="M129" s="45" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="130" spans="3:13" x14ac:dyDescent="0.3">
@@ -7448,10 +7348,10 @@
         <v>146</v>
       </c>
       <c r="L130" s="45" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="M130" s="45" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="131" spans="3:13" x14ac:dyDescent="0.3">
@@ -7459,10 +7359,10 @@
         <v>147</v>
       </c>
       <c r="L131" s="45" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="M131" s="45" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="132" spans="3:13" x14ac:dyDescent="0.3">
@@ -7470,10 +7370,10 @@
         <v>148</v>
       </c>
       <c r="L132" s="45" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="M132" s="45" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="133" spans="3:13" x14ac:dyDescent="0.3">
@@ -7481,10 +7381,10 @@
         <v>149</v>
       </c>
       <c r="L133" s="45" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="M133" s="45" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
     </row>
     <row r="134" spans="3:13" x14ac:dyDescent="0.3">
@@ -7492,10 +7392,10 @@
         <v>150</v>
       </c>
       <c r="L134" s="45" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="M134" s="45" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="135" spans="3:13" x14ac:dyDescent="0.3">
@@ -7503,10 +7403,10 @@
         <v>151</v>
       </c>
       <c r="L135" s="45" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="M135" s="45" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="136" spans="3:13" x14ac:dyDescent="0.3">
@@ -7514,10 +7414,10 @@
         <v>152</v>
       </c>
       <c r="L136" s="45" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="M136" s="45" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="137" spans="3:13" x14ac:dyDescent="0.3">
@@ -7525,10 +7425,10 @@
         <v>153</v>
       </c>
       <c r="L137" s="45" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="M137" s="45" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="138" spans="3:13" x14ac:dyDescent="0.3">
@@ -7536,10 +7436,10 @@
         <v>154</v>
       </c>
       <c r="L138" s="45" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="M138" s="45" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="139" spans="3:13" x14ac:dyDescent="0.3">
@@ -7547,10 +7447,10 @@
         <v>155</v>
       </c>
       <c r="L139" s="45" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="M139" s="45" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="140" spans="3:13" x14ac:dyDescent="0.3">
@@ -7558,10 +7458,10 @@
         <v>156</v>
       </c>
       <c r="L140" s="45" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="M140" s="45" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
     </row>
     <row r="141" spans="3:13" x14ac:dyDescent="0.3">
@@ -7569,10 +7469,10 @@
         <v>157</v>
       </c>
       <c r="L141" s="45" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="M141" s="45" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="142" spans="3:13" x14ac:dyDescent="0.3">
@@ -7580,10 +7480,10 @@
         <v>158</v>
       </c>
       <c r="L142" s="45" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="M142" s="45" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
     </row>
     <row r="143" spans="3:13" x14ac:dyDescent="0.3">
@@ -7591,10 +7491,10 @@
         <v>159</v>
       </c>
       <c r="L143" s="45" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="M143" s="45" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="144" spans="3:13" x14ac:dyDescent="0.3">
@@ -7602,10 +7502,10 @@
         <v>160</v>
       </c>
       <c r="L144" s="45" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="M144" s="45" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="145" spans="4:13" x14ac:dyDescent="0.3">
@@ -7613,10 +7513,10 @@
         <v>161</v>
       </c>
       <c r="L145" s="45" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="M145" s="45" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
     </row>
     <row r="146" spans="4:13" x14ac:dyDescent="0.3">
@@ -7624,10 +7524,10 @@
         <v>162</v>
       </c>
       <c r="L146" s="45" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="M146" s="45" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="147" spans="4:13" x14ac:dyDescent="0.3">
@@ -7635,10 +7535,10 @@
         <v>163</v>
       </c>
       <c r="L147" s="45" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="M147" s="45" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
     </row>
     <row r="148" spans="4:13" x14ac:dyDescent="0.3">
@@ -7646,10 +7546,10 @@
         <v>164</v>
       </c>
       <c r="L148" s="45" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="M148" s="45" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="149" spans="4:13" x14ac:dyDescent="0.3">
@@ -7657,10 +7557,10 @@
         <v>165</v>
       </c>
       <c r="L149" s="45" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="M149" s="45" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
     </row>
     <row r="150" spans="4:13" x14ac:dyDescent="0.3">
@@ -7668,10 +7568,10 @@
         <v>166</v>
       </c>
       <c r="L150" s="45" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="M150" s="45" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="151" spans="4:13" x14ac:dyDescent="0.3">
@@ -7679,10 +7579,10 @@
         <v>167</v>
       </c>
       <c r="L151" s="45" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="M151" s="45" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="152" spans="4:13" x14ac:dyDescent="0.3">
@@ -7690,10 +7590,10 @@
         <v>168</v>
       </c>
       <c r="L152" s="45" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="M152" s="45" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="153" spans="4:13" x14ac:dyDescent="0.3">
@@ -7701,10 +7601,10 @@
         <v>169</v>
       </c>
       <c r="L153" s="45" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="M153" s="45" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="154" spans="4:13" x14ac:dyDescent="0.3">
@@ -7712,10 +7612,10 @@
         <v>170</v>
       </c>
       <c r="L154" s="45" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="M154" s="45" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="155" spans="4:13" x14ac:dyDescent="0.3">
@@ -7723,10 +7623,10 @@
         <v>171</v>
       </c>
       <c r="L155" s="45" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="M155" s="45" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="156" spans="4:13" x14ac:dyDescent="0.3">
@@ -7734,10 +7634,10 @@
         <v>172</v>
       </c>
       <c r="L156" s="45" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="M156" s="45" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="157" spans="4:13" x14ac:dyDescent="0.3">
@@ -7745,10 +7645,10 @@
         <v>173</v>
       </c>
       <c r="L157" s="45" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="M157" s="45" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="158" spans="4:13" x14ac:dyDescent="0.3">
@@ -7756,10 +7656,10 @@
         <v>174</v>
       </c>
       <c r="L158" s="45" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="M158" s="45" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="159" spans="4:13" x14ac:dyDescent="0.3">
@@ -7767,10 +7667,10 @@
         <v>175</v>
       </c>
       <c r="L159" s="45" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="M159" s="45" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="160" spans="4:13" x14ac:dyDescent="0.3">
@@ -7778,10 +7678,10 @@
         <v>176</v>
       </c>
       <c r="L160" s="45" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="M160" s="45" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="161" spans="4:13" x14ac:dyDescent="0.3">
@@ -7789,10 +7689,10 @@
         <v>177</v>
       </c>
       <c r="L161" s="45" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="M161" s="45" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
     </row>
     <row r="162" spans="4:13" x14ac:dyDescent="0.3">
@@ -7800,10 +7700,10 @@
         <v>178</v>
       </c>
       <c r="L162" s="45" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="M162" s="45" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="163" spans="4:13" x14ac:dyDescent="0.3">
@@ -7811,10 +7711,10 @@
         <v>179</v>
       </c>
       <c r="L163" s="45" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="M163" s="45" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="164" spans="4:13" x14ac:dyDescent="0.3">
@@ -7822,10 +7722,10 @@
         <v>180</v>
       </c>
       <c r="L164" s="45" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="M164" s="45" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="165" spans="4:13" x14ac:dyDescent="0.3">
@@ -7833,10 +7733,10 @@
         <v>181</v>
       </c>
       <c r="L165" s="45" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="M165" s="45" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="166" spans="4:13" x14ac:dyDescent="0.3">
@@ -7844,10 +7744,10 @@
         <v>182</v>
       </c>
       <c r="L166" s="45" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="M166" s="45" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="167" spans="4:13" x14ac:dyDescent="0.3">
@@ -7855,10 +7755,10 @@
         <v>183</v>
       </c>
       <c r="L167" s="45" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="M167" s="45" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="168" spans="4:13" x14ac:dyDescent="0.3">
@@ -7866,10 +7766,10 @@
         <v>184</v>
       </c>
       <c r="L168" s="45" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="M168" s="45" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="169" spans="4:13" x14ac:dyDescent="0.3">
@@ -7877,10 +7777,10 @@
         <v>185</v>
       </c>
       <c r="L169" s="45" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M169" s="45" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="170" spans="4:13" x14ac:dyDescent="0.3">
@@ -7888,10 +7788,10 @@
         <v>186</v>
       </c>
       <c r="L170" s="45" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="M170" s="45" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="171" spans="4:13" x14ac:dyDescent="0.3">
@@ -7899,10 +7799,10 @@
         <v>187</v>
       </c>
       <c r="L171" s="45" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="M171" s="45" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="172" spans="4:13" x14ac:dyDescent="0.3">
@@ -7910,10 +7810,10 @@
         <v>188</v>
       </c>
       <c r="L172" s="45" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="M172" s="45" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="173" spans="4:13" x14ac:dyDescent="0.3">
@@ -7921,10 +7821,10 @@
         <v>189</v>
       </c>
       <c r="L173" s="45" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="M173" s="45" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="174" spans="4:13" x14ac:dyDescent="0.3">
@@ -7932,10 +7832,10 @@
         <v>190</v>
       </c>
       <c r="L174" s="45" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="M174" s="45" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
     </row>
     <row r="175" spans="4:13" x14ac:dyDescent="0.3">
@@ -7943,10 +7843,10 @@
         <v>191</v>
       </c>
       <c r="L175" s="45" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="M175" s="45" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="176" spans="4:13" x14ac:dyDescent="0.3">
@@ -7954,10 +7854,10 @@
         <v>192</v>
       </c>
       <c r="L176" s="45" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="M176" s="45" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="177" spans="3:13" x14ac:dyDescent="0.3">
@@ -7965,10 +7865,10 @@
         <v>193</v>
       </c>
       <c r="L177" s="45" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="M177" s="45" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="178" spans="3:13" x14ac:dyDescent="0.3">
@@ -7976,10 +7876,10 @@
         <v>194</v>
       </c>
       <c r="L178" s="45" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="M178" s="45" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="179" spans="3:13" x14ac:dyDescent="0.3">
@@ -7987,10 +7887,10 @@
         <v>195</v>
       </c>
       <c r="L179" s="45" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="M179" s="45" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="180" spans="3:13" x14ac:dyDescent="0.3">
@@ -7998,10 +7898,10 @@
         <v>196</v>
       </c>
       <c r="L180" s="45" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="M180" s="45" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="181" spans="3:13" x14ac:dyDescent="0.3">
@@ -8009,10 +7909,10 @@
         <v>197</v>
       </c>
       <c r="L181" s="45" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="M181" s="45" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="182" spans="3:13" x14ac:dyDescent="0.3">
@@ -8020,10 +7920,10 @@
         <v>198</v>
       </c>
       <c r="L182" s="45" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="M182" s="45" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="183" spans="3:13" x14ac:dyDescent="0.3">
@@ -8031,10 +7931,10 @@
         <v>199</v>
       </c>
       <c r="L183" s="45" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="M183" s="45" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="184" spans="3:13" x14ac:dyDescent="0.3">
@@ -8042,10 +7942,10 @@
         <v>200</v>
       </c>
       <c r="L184" s="45" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="M184" s="45" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="185" spans="3:13" x14ac:dyDescent="0.3">
@@ -8053,10 +7953,10 @@
         <v>201</v>
       </c>
       <c r="L185" s="45" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="M185" s="45" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="186" spans="3:13" x14ac:dyDescent="0.3">
@@ -8064,10 +7964,10 @@
         <v>202</v>
       </c>
       <c r="L186" s="45" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="M186" s="45" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="187" spans="3:13" x14ac:dyDescent="0.3">
@@ -8075,10 +7975,10 @@
         <v>203</v>
       </c>
       <c r="L187" s="45" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="M187" s="45" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="188" spans="3:13" x14ac:dyDescent="0.3">
@@ -8086,10 +7986,10 @@
         <v>204</v>
       </c>
       <c r="L188" s="45" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="M188" s="45" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="189" spans="3:13" x14ac:dyDescent="0.3">
@@ -8097,10 +7997,10 @@
         <v>205</v>
       </c>
       <c r="L189" s="45" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="M189" s="45" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="190" spans="3:13" x14ac:dyDescent="0.3">
@@ -8108,10 +8008,10 @@
         <v>206</v>
       </c>
       <c r="L190" s="45" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="M190" s="45" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="191" spans="3:13" x14ac:dyDescent="0.3">
@@ -8119,24 +8019,24 @@
         <v>207</v>
       </c>
       <c r="L191" s="45" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="M191" s="45" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="192" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C192" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D192" t="s">
         <v>208</v>
       </c>
       <c r="L192" s="45" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="M192" s="45" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="193" spans="3:13" x14ac:dyDescent="0.3">
@@ -8144,10 +8044,10 @@
         <v>209</v>
       </c>
       <c r="L193" s="45" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="M193" s="45" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="194" spans="3:13" x14ac:dyDescent="0.3">
@@ -8155,24 +8055,24 @@
         <v>210</v>
       </c>
       <c r="L194" s="45" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="M194" s="45" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="195" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C195" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D195" t="s">
         <v>211</v>
       </c>
       <c r="L195" s="45" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="M195" s="45" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
     </row>
     <row r="196" spans="3:13" x14ac:dyDescent="0.3">
@@ -8180,1382 +8080,1382 @@
         <v>212</v>
       </c>
       <c r="L196" s="45" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="M196" s="45" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="197" spans="3:13" x14ac:dyDescent="0.3">
       <c r="L197" s="45" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="M197" s="45" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
     </row>
     <row r="198" spans="3:13" x14ac:dyDescent="0.3">
       <c r="L198" s="45" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="M198" s="45" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="199" spans="3:13" x14ac:dyDescent="0.3">
       <c r="L199" s="45" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="M199" s="45" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="200" spans="3:13" x14ac:dyDescent="0.3">
       <c r="L200" s="45" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="M200" s="45" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="201" spans="3:13" x14ac:dyDescent="0.3">
       <c r="L201" s="45" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="M201" s="45" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="202" spans="3:13" x14ac:dyDescent="0.3">
       <c r="L202" s="45" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="M202" s="45" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="203" spans="3:13" x14ac:dyDescent="0.3">
       <c r="L203" s="45" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="M203" s="45" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
     </row>
     <row r="204" spans="3:13" x14ac:dyDescent="0.3">
       <c r="L204" s="45" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="M204" s="45" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="205" spans="3:13" x14ac:dyDescent="0.3">
       <c r="L205" s="45" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="M205" s="45" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
     </row>
     <row r="206" spans="3:13" x14ac:dyDescent="0.3">
       <c r="L206" s="45" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="M206" s="45" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
     </row>
     <row r="207" spans="3:13" x14ac:dyDescent="0.3">
       <c r="L207" s="45" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="M207" s="45" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="208" spans="3:13" x14ac:dyDescent="0.3">
       <c r="L208" s="45" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M208" s="45" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
     </row>
     <row r="209" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L209" s="45" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="M209" s="45" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="210" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L210" s="45" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="M210" s="45" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
     </row>
     <row r="211" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L211" s="45" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="M211" s="45" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
     </row>
     <row r="212" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L212" s="45" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="M212" s="45" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
     </row>
     <row r="213" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L213" s="45" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="M213" s="45" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="214" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L214" s="45" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="M214" s="45" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="215" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L215" s="45" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="M215" s="45" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="216" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L216" s="45" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="M216" s="45" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="217" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L217" s="45" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="M217" s="45" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="218" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L218" s="45" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="M218" s="45" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
     </row>
     <row r="219" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L219" s="45" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="M219" s="45" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="220" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L220" s="45" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M220" s="45" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
     </row>
     <row r="221" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L221" s="45" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="M221" s="45" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
     </row>
     <row r="222" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L222" s="45" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="M222" s="45" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
     </row>
     <row r="223" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L223" s="45" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="M223" s="45" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
     </row>
     <row r="224" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L224" s="45" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="M224" s="45" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="225" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L225" s="45" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="M225" s="45" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
     </row>
     <row r="226" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L226" s="45" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="M226" s="45" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="227" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L227" s="45" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="M227" s="45" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="228" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L228" s="45" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="M228" s="45" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
     </row>
     <row r="229" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L229" s="45" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="M229" s="45" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
     </row>
     <row r="230" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L230" s="45" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="M230" s="45" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
     </row>
     <row r="231" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L231" s="45" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="M231" s="45" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
     </row>
     <row r="232" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L232" s="45" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="M232" s="45" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
     </row>
     <row r="233" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L233" s="45" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="M233" s="45" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="234" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L234" s="45" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="M234" s="45" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
     </row>
     <row r="235" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L235" s="45" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="M235" s="45" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="236" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L236" s="45" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="M236" s="45" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
     </row>
     <row r="237" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L237" s="45" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="M237" s="45" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="238" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L238" s="45" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="M238" s="45" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="239" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L239" s="45" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="M239" s="45" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
     </row>
     <row r="240" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L240" s="45" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="M240" s="45" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
     </row>
     <row r="241" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L241" s="45" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="M241" s="45" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="242" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L242" s="45" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="M242" s="45" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="243" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L243" s="45" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="M243" s="45" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="244" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L244" s="45" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="M244" s="45" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="245" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L245" s="45" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="M245" s="45" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
     </row>
     <row r="246" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L246" s="45" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="M246" s="45" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="247" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L247" s="45" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="M247" s="45" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="248" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L248" s="45" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="M248" s="45" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="249" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L249" s="45" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="M249" s="45" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="250" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L250" s="45" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="M250" s="45" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="251" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L251" s="45" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="M251" s="45" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="252" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L252" s="45" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="M252" s="45" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="253" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L253" s="45" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="M253" s="45" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="254" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L254" s="45" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="M254" s="45" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="255" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L255" s="45" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="M255" s="45" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="256" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L256" s="45" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="M256" s="45" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="257" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L257" s="45" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="M257" s="45" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="258" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L258" s="45" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="M258" s="45" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
     </row>
     <row r="259" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L259" s="45" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="M259" s="45" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
     </row>
     <row r="260" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L260" s="45" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="M260" s="45" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="261" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L261" s="45" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="M261" s="45" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="262" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L262" s="45" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="M262" s="45" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="263" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L263" s="45" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="M263" s="45" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="264" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L264" s="45" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="M264" s="45" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
     </row>
     <row r="265" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L265" s="45" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="M265" s="45" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
     </row>
     <row r="266" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L266" s="45" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="M266" s="45" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="267" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L267" s="45" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="M267" s="45" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
     </row>
     <row r="268" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L268" s="45" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="M268" s="45" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="269" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L269" s="45" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="M269" s="45" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
     </row>
     <row r="270" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L270" s="45" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="M270" s="45" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
     <row r="271" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L271" s="45" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="M271" s="45" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="272" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L272" s="45" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="M272" s="45" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="273" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L273" s="45" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="M273" s="45" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="274" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L274" s="45" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="M274" s="45" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
     </row>
     <row r="275" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L275" s="45" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="M275" s="45" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="276" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L276" s="45" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="M276" s="45" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="277" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L277" s="45" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="M277" s="45" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="278" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L278" s="45" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="M278" s="45" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="279" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L279" s="45" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="M279" s="45" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
     <row r="280" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L280" s="45" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="M280" s="45" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="281" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L281" s="45" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="M281" s="45" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
     </row>
     <row r="282" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L282" s="45" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="M282" s="45" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="283" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L283" s="45" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="M283" s="45" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="284" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L284" s="45" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="M284" s="45" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="285" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L285" s="45" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="M285" s="45" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
     </row>
     <row r="286" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L286" s="45" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="M286" s="45" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="287" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L287" s="45" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="M287" s="45" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="288" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L288" s="45" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="M288" s="45" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="289" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L289" s="45" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="M289" s="45" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
     </row>
     <row r="290" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L290" s="45" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="M290" s="45" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="291" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L291" s="45" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="M291" s="45" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
     </row>
     <row r="292" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L292" s="45" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="M292" s="45" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="293" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L293" s="45" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="M293" s="45" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
     </row>
     <row r="294" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L294" s="45" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="M294" s="45" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="295" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L295" s="45" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="M295" s="45" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
     </row>
     <row r="296" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L296" s="45" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="M296" s="45" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
     </row>
     <row r="297" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L297" s="45" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="M297" s="45" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="298" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L298" s="45" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="M298" s="45" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="299" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L299" s="45" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="M299" s="45" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="300" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L300" s="45" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="M300" s="45" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="301" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L301" s="45" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="M301" s="45" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="302" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L302" s="45" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="M302" s="45" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
     </row>
     <row r="303" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L303" s="45" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="M303" s="45" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="304" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L304" s="45" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="M304" s="45" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
     </row>
     <row r="305" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L305" s="45" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="M305" s="45" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
     </row>
     <row r="306" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L306" s="45" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="M306" s="45" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="307" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L307" s="45" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="M307" s="45" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="308" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L308" s="45" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="M308" s="45" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="309" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L309" s="45" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="M309" s="45" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="310" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L310" s="45" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="M310" s="45" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
     </row>
     <row r="311" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L311" s="45" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="M311" s="45" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
     </row>
     <row r="312" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L312" s="45" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="M312" s="45" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="313" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L313" s="45" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="M313" s="45" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
     </row>
     <row r="314" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L314" s="45" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="M314" s="45" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="315" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L315" s="45" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="M315" s="45" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="316" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L316" s="45" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="M316" s="45" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="317" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L317" s="45" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="M317" s="45" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
     </row>
     <row r="318" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L318" s="45" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="M318" s="45" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
     </row>
     <row r="319" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L319" s="45" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="M319" s="45" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="320" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L320" s="45" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="M320" s="45" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="321" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L321" s="45" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="M321" s="45" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="322" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L322" s="45" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="M322" s="45" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="323" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L323" s="45" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="M323" s="45" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
     </row>
     <row r="324" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L324" s="45" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="M324" s="45" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
     </row>
     <row r="325" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L325" s="45" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="M325" s="45" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="326" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L326" s="45" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="M326" s="45" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
     </row>
     <row r="327" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L327" s="45" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="M327" s="45" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
     </row>
     <row r="328" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L328" s="45" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="M328" s="45" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="329" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L329" s="45" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="M329" s="45" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
     </row>
     <row r="330" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L330" s="45" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="M330" s="45" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
     </row>
     <row r="331" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L331" s="45" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="M331" s="45" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
     </row>
     <row r="332" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L332" s="45" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="M332" s="45" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
     </row>
     <row r="333" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L333" s="45" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="M333" s="45" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
     </row>
     <row r="334" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L334" s="45" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="M334" s="45" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
     </row>
     <row r="335" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L335" s="45" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="M335" s="45" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
     </row>
     <row r="336" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L336" s="45" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="M336" s="45" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
     </row>
     <row r="337" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L337" s="45" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="M337" s="45" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="338" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L338" s="45" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="M338" s="45" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="339" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L339" s="45" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="M339" s="45" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="340" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L340" s="45" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="M340" s="45" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
     </row>
     <row r="341" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L341" s="45" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="M341" s="45" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="342" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L342" s="45" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="M342" s="45" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
     </row>
     <row r="343" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L343" s="45" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="M343" s="45" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="344" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L344" s="45" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="M344" s="45" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
     </row>
     <row r="345" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L345" s="45" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="M345" s="45" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="346" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L346" s="45" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="M346" s="45" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="347" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L347" s="45" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="M347" s="45" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="348" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L348" s="45" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="M348" s="45" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
     </row>
     <row r="349" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L349" s="45" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="M349" s="45" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="350" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L350" s="45" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="M350" s="45" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
     </row>
     <row r="351" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L351" s="45" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="M351" s="45" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
     </row>
     <row r="352" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L352" s="45" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M352" s="45" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="353" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L353" s="45" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="M353" s="45" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="354" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L354" s="45" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="M354" s="45" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
     </row>
     <row r="355" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L355" s="45" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="M355" s="45" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
     </row>
     <row r="356" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L356" s="45" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="M356" s="45" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="357" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L357" s="45" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="M357" s="45" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="358" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L358" s="45" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="M358" s="45" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
     </row>
     <row r="359" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L359" s="45" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="M359" s="45" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="360" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L360" s="45" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="M360" s="45" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="361" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L361" s="45" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="M361" s="45" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
     </row>
     <row r="362" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L362" s="45" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="M362" s="45" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="363" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L363" s="45" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="M363" s="45" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="364" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L364" s="45" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="M364" s="45" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="365" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L365" s="45" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="M365" s="45" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
     </row>
     <row r="366" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L366" s="45" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="M366" s="45" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="367" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L367" s="45" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="M367" s="45" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="L5vAye0TbAAC8Qm8FDf4WRgLPgaIrH52OU4QVTrTWcd7gJf/DRa+5BiKeqkc9PJOomtBsojduKnq1B4AlWNd+w==" saltValue="+vo/e5yxWI6ZgRq2UDrlKw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="JuvFdip5Y5t3MezcvCCc9TG4FmooXW1thZwWmKC3PW7bX3U653qLuRyOdr6pw0eijzVjuBwoKe2ZWo2QK7ttjw==" saltValue="CEMeiSLjn3WroypoUs5Olw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <autoFilter ref="C2:M196" xr:uid="{00000000-0001-0000-0100-000000000000}">
     <filterColumn colId="6" showButton="0"/>
   </autoFilter>

--- a/public/docs/Plantilla Cursos Extensión.xlsx
+++ b/public/docs/Plantilla Cursos Extensión.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://escuelanaval-my.sharepoint.com/personal/jestadisticaplen_enap_edu_co/Documents/Estadística/Plantillas Xertify/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\planeacionenap\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="270" documentId="13_ncr:1_{BC3BDC5F-05B6-4C86-84AC-9E3B4D15C583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57AEF430-EAAD-4D7F-AF76-556C305AB0DA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0122E598-D09C-49DC-99A8-6EC15D2B76AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5856,7 +5856,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="C1:M367"/>
+  <dimension ref="A1:M367"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="10.5" customWidth="1"/>
@@ -5867,16 +5867,16 @@
     <col min="13" max="13" width="17.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="E1" s="46" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="46" t="s">
         <v>972</v>
       </c>
     </row>
-    <row r="2" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="I2" s="47"/>
       <c r="J2" s="47"/>
     </row>
-    <row r="3" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D3" s="1" t="s">
         <v>19</v>
       </c>
@@ -5894,7 +5894,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="4" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
         <v>21</v>
       </c>
@@ -5911,7 +5911,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="5" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
         <v>23</v>
       </c>
@@ -5928,7 +5928,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="6" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
         <v>24</v>
       </c>
@@ -5942,7 +5942,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="7" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
         <v>25</v>
       </c>
@@ -5956,7 +5956,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="8" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
         <v>26</v>
       </c>
@@ -5967,7 +5967,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="9" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
         <v>27</v>
       </c>
@@ -5978,7 +5978,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="10" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
         <v>28</v>
       </c>
@@ -5989,7 +5989,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="11" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>239</v>
       </c>
@@ -6003,7 +6003,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="12" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
         <v>30</v>
       </c>
@@ -6014,7 +6014,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="13" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
         <v>31</v>
       </c>
@@ -6025,7 +6025,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="14" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
         <v>32</v>
       </c>
@@ -6036,7 +6036,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="15" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
         <v>33</v>
       </c>
@@ -6047,7 +6047,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="16" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
         <v>34</v>
       </c>
@@ -9455,7 +9455,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="JuvFdip5Y5t3MezcvCCc9TG4FmooXW1thZwWmKC3PW7bX3U653qLuRyOdr6pw0eijzVjuBwoKe2ZWo2QK7ttjw==" saltValue="CEMeiSLjn3WroypoUs5Olw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="7R2Wx+gkR4TOjTtl9VG745xyylvkAZwoPiOj1j3xEzVwL2c4wNehh58xyGWSyffjb52wdVfcIDeBA3XN9XJZMg==" saltValue="DbtXDbJA69yxTeahXxp1bw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <autoFilter ref="C2:M196" xr:uid="{00000000-0001-0000-0100-000000000000}">
     <filterColumn colId="6" showButton="0"/>
   </autoFilter>

--- a/public/docs/Plantilla Cursos Extensión.xlsx
+++ b/public/docs/Plantilla Cursos Extensión.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\planeacionenap\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://escuelanaval-my.sharepoint.com/personal/jestadisticaplen_enap_edu_co/Documents/Estadística/Plantillas Xertify/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0122E598-D09C-49DC-99A8-6EC15D2B76AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{0122E598-D09C-49DC-99A8-6EC15D2B76AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1165363E-E662-46BF-97C0-C1BDAB471AFE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5179,7 +5179,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>(Ejemplo: 06 de mayo de 2025)</a:t>
+            <a:t>(Ejemplo: 6 de mayo de 2025)</a:t>
           </a:r>
           <a:endParaRPr lang="es-CO" sz="1100" b="0">
             <a:solidFill>
@@ -5294,9 +5294,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5334,7 +5334,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5440,7 +5440,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5582,7 +5582,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5808,7 +5808,7 @@
       <c r="Z3" s="29"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="oRHisi8i6cl25vIdOGc5S6pQT1PrOi33JBM6FxjQdwp4cyXeFjS1kqQeY5oAtVhRbnRiL8IK/sY3O6bFfNU1OA==" saltValue="WMhulMvucZopm2IUsk/VWg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="X5YGJzxjKWw7h4Va5zE/rgZorF6zMBWUzczQN2yy5TfxFBhWFey3WUaHQgvjcSeO6fabLon7gv1RRw282MJT4Q==" saltValue="FEyIGD/wo9Jh7Fa2bPPNZg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
     <protectedRange sqref="A3:Z422" name="Rango1"/>
   </protectedRanges>
